--- a/etf_holdings/2026-10-30_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.41%2415</t>
+          <t>-1.86%2370</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2415</v>
+        <v>2370</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.72%1,680,000</t>
+          <t>13.89%1,680,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.72%</t>
+          <t>13.89%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.33%1885</t>
+          <t>-1.41%6315</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1885</v>
+        <v>6315</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.78%575,036</t>
+          <t>3.20%146,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>575036</v>
+        <v>146000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.74%5190</t>
+          <t>-4.03%1190</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.74%</t>
+          <t>-4.03%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5190</v>
+        <v>1190</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.15%168,000</t>
+          <t>3.03%713,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>168000</v>
+        <v>713000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.47%6405</t>
+          <t>-3.27%207</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6405</v>
+        <v>207</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.13%146,000</t>
+          <t>3.03%4,137,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>146000</v>
+        <v>4137000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.38%214</t>
+          <t>-3.98%1810</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>214</v>
+        <v>1810</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.02%4,137,000</t>
+          <t>2.99%463,036</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4137000</v>
+        <v>463036</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4904遠傳</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.89%113</t>
+          <t>-4.62%4950</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-4.62%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>113</v>
+        <v>4950</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.80%7,423,000</t>
+          <t>2.99%168,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>7423000</v>
+        <v>168000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.3%5010</t>
+          <t>-6.69%4675</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-6.69%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5010</v>
+        <v>4675</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.79%165,000</t>
+          <t>2.83%165,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.31%1755</t>
+          <t>-9.8%1335</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1755</v>
+        <v>1335</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.46%403,000</t>
+          <t>2.68%528,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>403000</v>
+        <v>528000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1216統一</t>
+          <t>4904遠傳</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.38%79</t>
+          <t>+0.88%114</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.45%9,243,000</t>
+          <t>2.50%6,471,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>9243000</v>
+        <v>6471000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.33%1240</t>
+          <t>-7.98%1615</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>-7.98%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1240</v>
+        <v>1615</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.44%605,000</t>
+          <t>2.42%403,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>605000</v>
+        <v>403000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.52%1480</t>
+          <t>-2.33%9650</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1480</v>
+        <v>9650</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.41%462,000</t>
+          <t>2.30%68,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>462000</v>
+        <v>68000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2412中華電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.66%9880</t>
+          <t>+1.27%160</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.66%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9880</v>
+        <v>160</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.32%68,000</t>
+          <t>2.22%4,107,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>68000</v>
+        <v>4107000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>1216統一</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-5.38%343</t>
+          <t>+1.52%80.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>343</v>
+        <v>80.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.16%1,769,000</t>
+          <t>2.20%8,135,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1769000</v>
+        <v>8135000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.96%158</t>
+          <t>-2.04%336</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>158</v>
+        <v>336</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.16%4,107,000</t>
+          <t>2.08%1,769,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4107000</v>
+        <v>1769000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:17</t>
+          <t>2026-10-30 23:08:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-5.45%1040</t>
+          <t>-7.96%2370</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-7.96%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1040</v>
+        <v>2370</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.06%555,000</t>
+          <t>2.00%227,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>555000</v>
+        <v>227000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.18%50.4</t>
+          <t>-0.4%50.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.99%11,562,000</t>
+          <t>2.00%11,562,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.19%2575</t>
+          <t>-4.9%989</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2575</v>
+        <v>989</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.97%227,000</t>
+          <t>1.98%555,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>227000</v>
+        <v>555000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.39%248</t>
+          <t>-1.01%245.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>248</v>
+        <v>245.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.88%2,225,000</t>
+          <t>1.89%2,225,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.73%543</t>
+          <t>-7.55%502</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-7.55%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.84%999,000</t>
+          <t>1.86%999,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>1101台泥</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-8.21%5815</t>
+          <t>+0.53%28.35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.21%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5815</v>
+        <v>28.35</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.79%84,000</t>
+          <t>1.82%18,842,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>84000</v>
+        <v>18842000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,25 +1724,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1101台泥</t>
+          <t>2610華航</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.71%28.2</t>
+          <t>-0.49%20.15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>28.2</v>
+        <v>20.15</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.78%18,842,000</t>
+          <t>1.78%25,735,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1751,11 +1751,11 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>18842000</v>
+        <v>25735000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2610華航</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0%20.25</t>
+          <t>-3.21%3915</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>20.25</v>
+        <v>3915</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.75%25,735,000</t>
+          <t>1.74%126,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>25735000</v>
+        <v>126000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.71%28.35</t>
+          <t>-0.35%28.25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>28.35</v>
+        <v>28.25</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.70%17,903,000</t>
+          <t>1.74%17,903,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.73%683</t>
+          <t>-3.46%111.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>683</v>
+        <v>111.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.65%704,000</t>
+          <t>1.69%4,268,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>704000</v>
+        <v>4268000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.87%170.5</t>
+          <t>-6.62%5430</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>170.5</v>
+        <v>5430</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.56%2,698,000</t>
+          <t>1.67%84,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2698000</v>
+        <v>84000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.49%4045</t>
+          <t>-2.2%668</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.49%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4045</v>
+        <v>668</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.45%102,000</t>
+          <t>1.65%704,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>102000</v>
+        <v>704000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,34 +2090,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-4.12%814</t>
+          <t>-3.52%164.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-4.12%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>814</v>
+        <v>164.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.41%492,000</t>
+          <t>1.57%2,698,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>492000</v>
+        <v>2698000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.76%261</t>
+          <t>-4.69%1625</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>261</v>
+        <v>1625</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.39%1,569,000</t>
+          <t>1.51%258,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1569000</v>
+        <v>258000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.8%37.25</t>
+          <t>-3.49%35.95</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>37.25</v>
+        <v>35.95</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.39%10,998,000</t>
+          <t>1.40%10,998,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:19</t>
+          <t>2026-10-30 23:08:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2609陽明</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.43%62</t>
+          <t>+4.02%271.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>+4.02%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>62</v>
+        <v>271.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.37%6,482,000</t>
+          <t>1.40%1,569,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>6482000</v>
+        <v>1569000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2609陽明</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0%477</t>
+          <t>+2.42%63.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>477</v>
+        <v>63.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.34%833,000</t>
+          <t>1.38%6,482,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>833000</v>
+        <v>6482000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-9.77%115.5</t>
+          <t>-7.13%756</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-9.77%</t>
+          <t>-7.13%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>115.5</v>
+        <v>756</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.34%3,110,000</t>
+          <t>1.37%492,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>3110000</v>
+        <v>492000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.24%841</t>
+          <t>-4.72%454.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-4.72%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>841</v>
+        <v>454.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.30%457,000</t>
+          <t>1.36%833,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>457000</v>
+        <v>833000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-5.8%1705</t>
+          <t>-7.73%776</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-7.73%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1705</v>
+        <v>776</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.29%211,000</t>
+          <t>1.32%457,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>211000</v>
+        <v>457000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-5.91%1115</t>
+          <t>-2.63%2035</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1115</v>
+        <v>2035</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.24%311,000</t>
+          <t>1.31%183,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>311000</v>
+        <v>183000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3105穩懋</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+10%594</t>
+          <t>-8.52%1020</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-8.52%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>594</v>
+        <v>1020</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.21%666,000</t>
+          <t>1.19%311,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>666000</v>
+        <v>311000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.42%3105</t>
+          <t>-0.32%3095</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3105</v>
+        <v>3095</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.18%109,000</t>
+          <t>1.16%109,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-3.08%188.5</t>
+          <t>-2.65%183.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>188.5</v>
+        <v>183.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.01%1,538,000</t>
+          <t>0.99%1,538,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-7.12%1305</t>
+          <t>-5.75%1230</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-7.12%</t>
+          <t>-5.75%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1305</v>
+        <v>1230</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.95%201,000</t>
+          <t>0.90%201,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+4.24%2090</t>
+          <t>-1.56%157.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+4.24%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2090</v>
+        <v>157.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.89%132,000</t>
+          <t>0.86%1,576,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>132000</v>
+        <v>1576000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>6526達發</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-5.04%160</t>
+          <t>-1.42%765</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.04%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>160</v>
+        <v>765</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.89%1,576,000</t>
+          <t>0.83%314,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1576000</v>
+        <v>314000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6526達發</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.36%776</t>
+          <t>-6.37%213</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.36%</t>
+          <t>-6.37%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>776</v>
+        <v>213</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.85%314,000</t>
+          <t>0.73%934,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>314000</v>
+        <v>934000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-3.81%227.5</t>
+          <t>-6.93%3425</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.81%</t>
+          <t>-6.93%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>227.5</v>
+        <v>3425</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.74%934,000</t>
+          <t>0.64%51,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>934000</v>
+        <v>51000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>1504東元</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-3.16%3680</t>
+          <t>-0.58%69.1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3680</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.65%51,000</t>
+          <t>0.52%2,177,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>51000</v>
+        <v>2177000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:20</t>
+          <t>2026-10-30 23:08:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-7.34%959</t>
+          <t>-2.82%932</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-7.34%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>959</v>
+        <v>932</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.52%149,000</t>
+          <t>0.49%149,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:21</t>
+          <t>2026-10-30 23:08:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,34 +3249,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1504東元</t>
+          <t>1301台塑</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1%69.5</t>
+          <t>-1.89%72.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-1.89%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.51%2,177,000</t>
+          <t>0.44%1,724,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>2177000</v>
+        <v>1724000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:21</t>
+          <t>2026-10-30 23:08:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1301台塑</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.99%73.9</t>
+          <t>-2.71%1255</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>73.90000000000001</v>
+        <v>1255</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.44%1,724,000</t>
+          <t>0.18%40,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1724000</v>
+        <v>40000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:21</t>
+          <t>2026-10-30 23:08:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-3.73%1290</t>
+          <t>-2.69%578</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-3.73%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1290</v>
+        <v>578</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.18%40,000</t>
+          <t>0.10%49,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>40000</v>
+        <v>49000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:21</t>
+          <t>2026-10-30 23:08:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-3.85%1250</t>
+          <t>-4.8%1190</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1250</v>
+        <v>1190</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:21</t>
+          <t>2026-10-30 23:08:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.52%1545</t>
+          <t>-7.12%1435</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-7.12%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1545</v>
+        <v>1435</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-30_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:34</t>
+          <t>2026-10-30 23:20:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:35</t>
+          <t>2026-10-30 23:20:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:37</t>
+          <t>2026-10-30 23:20:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:38</t>
+          <t>2026-10-30 23:20:22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:38</t>
+          <t>2026-10-30 23:20:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:38</t>
+          <t>2026-10-30 23:20:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:38</t>
+          <t>2026-10-30 23:20:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:38</t>
+          <t>2026-10-30 23:20:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-30_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:18</t>
+          <t>2026-10-30 23:56:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:20</t>
+          <t>2026-10-30 23:56:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:21</t>
+          <t>2026-10-30 23:56:34</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:22</t>
+          <t>2026-10-30 23:56:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:22</t>
+          <t>2026-10-30 23:56:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:22</t>
+          <t>2026-10-30 23:56:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:22</t>
+          <t>2026-10-30 23:56:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:22</t>
+          <t>2026-10-30 23:56:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
